--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_2_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_2_branch.xlsx
@@ -646,49 +646,49 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.282962610066685</v>
+        <v>4.282962610066692</v>
       </c>
       <c r="C2">
-        <v>4.282962610066685</v>
+        <v>4.282962610066692</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9.277811204449902</v>
+        <v>9.277811204449907</v>
       </c>
       <c r="F2">
-        <v>148.3661769510661</v>
+        <v>148.3661769510664</v>
       </c>
       <c r="G2">
-        <v>148.3661769510661</v>
+        <v>148.3661769510664</v>
       </c>
       <c r="H2">
-        <v>28.61627979050437</v>
+        <v>28.61627979050436</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>32.46847082824991</v>
+        <v>32.46847082824975</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-77.7798457942141</v>
+        <v>-77.77984579421407</v>
       </c>
       <c r="M2">
         <v>102.2201542057786</v>
       </c>
       <c r="N2">
-        <v>0.2917056037382965</v>
+        <v>0.2917056037382951</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-29.1713773552604</v>
+        <v>-29.17137735526048</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -843,88 +843,88 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.709154423744983</v>
+        <v>3.709154423744981</v>
       </c>
       <c r="D2">
-        <v>3.709154423744982</v>
+        <v>3.709154423744984</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
+        <v>3.709154423744978</v>
+      </c>
+      <c r="G2">
         <v>3.709154423744981</v>
       </c>
-      <c r="G2">
-        <v>3.709154423744979</v>
-      </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>42.82962610030115</v>
+        <v>42.82962610030112</v>
       </c>
       <c r="J2">
-        <v>42.82962610030114</v>
+        <v>42.82962610030116</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
+        <v>42.82962610030109</v>
+      </c>
+      <c r="M2">
         <v>42.82962610030112</v>
       </c>
-      <c r="M2">
-        <v>42.8296261003011</v>
-      </c>
       <c r="N2">
-        <v>-1.563194052542778E-14</v>
+        <v>-2.084258736723711E-14</v>
       </c>
       <c r="O2">
         <v>30.17661447772223</v>
       </c>
       <c r="P2">
-        <v>-15.86847458187514</v>
+        <v>-15.86847458187516</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>5.21064684180933E-15</v>
       </c>
       <c r="R2">
         <v>-23.02254452973953</v>
       </c>
       <c r="S2">
-        <v>23.02254452985794</v>
+        <v>23.02254452985798</v>
       </c>
       <c r="T2">
-        <v>-5.210646841809429E-15</v>
+        <v>-2.101449535671551E-28</v>
       </c>
       <c r="U2">
-        <v>3.130989834187389</v>
+        <v>3.13098983418739</v>
       </c>
       <c r="V2">
-        <v>13.10324558045218</v>
+        <v>13.10324558045217</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>-5.210646841809223E-15</v>
       </c>
       <c r="X2">
-        <v>4.986127873134734</v>
+        <v>4.986127873134726</v>
       </c>
       <c r="Y2">
-        <v>-4.986127873130088</v>
+        <v>-4.986127873130072</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-167.7798457937528</v>
+        <v>-167.7798457937527</v>
       </c>
       <c r="AB2">
-        <v>12.22015420623994</v>
+        <v>12.22015420623991</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>12.2201542062399</v>
+        <v>12.22015420623995</v>
       </c>
       <c r="AE2">
         <v>-167.7798457937528</v>
@@ -933,22 +933,22 @@
         <v>1.10000002383429</v>
       </c>
       <c r="AG2">
-        <v>0.7083556674758259</v>
+        <v>0.7083556674758261</v>
       </c>
       <c r="AH2">
-        <v>0.4804898682203931</v>
+        <v>0.4804898682203932</v>
       </c>
       <c r="AI2">
         <v>1.10000002383429</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000119158041</v>
+        <v>0.5500000119158045</v>
       </c>
       <c r="AK2">
-        <v>0.5500000119184835</v>
+        <v>0.550000011918484</v>
       </c>
       <c r="AL2">
-        <v>5.539583542744682E-13</v>
+        <v>5.776835050861648E-13</v>
       </c>
       <c r="AM2">
         <v>-161.8562887546276</v>
@@ -957,10 +957,10 @@
         <v>152.6722796269628</v>
       </c>
       <c r="AO2">
-        <v>5.579346595365287E-13</v>
+        <v>5.863852980077035E-13</v>
       </c>
       <c r="AP2">
-        <v>179.999999999954</v>
+        <v>179.9999999999541</v>
       </c>
       <c r="AQ2">
         <v>-179.9999999999593</v>
@@ -1115,73 +1115,73 @@
         <v>0</v>
       </c>
       <c r="C2">
+        <v>1.763086650584201</v>
+      </c>
+      <c r="D2">
+        <v>1.763086650584201</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>1.7630866505842</v>
       </c>
-      <c r="D2">
-        <v>1.763086650584199</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1.763086650584199</v>
-      </c>
       <c r="G2">
-        <v>1.763086650584199</v>
+        <v>1.7630866505842</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
+        <v>20.35837104638848</v>
+      </c>
+      <c r="J2">
+        <v>20.35837104638848</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>20.35837104638848</v>
+      </c>
+      <c r="M2">
         <v>20.35837104638847</v>
       </c>
-      <c r="J2">
-        <v>20.35837104638846</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>20.35837104638846</v>
-      </c>
-      <c r="M2">
-        <v>20.35837104638846</v>
-      </c>
       <c r="N2">
-        <v>-5.210646841828691E-15</v>
+        <v>-5.21064684182868E-15</v>
       </c>
       <c r="O2">
         <v>19.0760556007627</v>
       </c>
       <c r="P2">
-        <v>-0.3008693307267596</v>
+        <v>-0.3008693307267467</v>
       </c>
       <c r="Q2">
-        <v>-1.065077804925686E-29</v>
+        <v>-1.058558377854652E-29</v>
       </c>
       <c r="R2">
-        <v>-17.4596488079289</v>
+        <v>-17.45964880792892</v>
       </c>
       <c r="S2">
-        <v>1.917276123560544</v>
+        <v>1.917276123560542</v>
       </c>
       <c r="T2">
-        <v>-2.099883541352902E-29</v>
+        <v>-2.605323420914366E-15</v>
       </c>
       <c r="U2">
-        <v>3.991912765039887</v>
+        <v>3.991912765039883</v>
       </c>
       <c r="V2">
-        <v>15.21845990328566</v>
+        <v>15.21845990328568</v>
       </c>
       <c r="W2">
-        <v>2.605323420914345E-15</v>
+        <v>2.605323420914346E-15</v>
       </c>
       <c r="X2">
-        <v>-2.15791277681687</v>
+        <v>-2.15791277681686</v>
       </c>
       <c r="Y2">
-        <v>-13.38445991506266</v>
+        <v>-13.38445991506267</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1190,13 +1190,13 @@
         <v>-149.9129785515271</v>
       </c>
       <c r="AB2">
-        <v>30.08702144846557</v>
+        <v>30.08702144846561</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>30.08702144846557</v>
+        <v>30.08702144846561</v>
       </c>
       <c r="AE2">
         <v>-149.9129785515271</v>
@@ -1205,7 +1205,7 @@
         <v>1.100000023838388</v>
       </c>
       <c r="AG2">
-        <v>0.9573094133256667</v>
+        <v>0.9573094133256668</v>
       </c>
       <c r="AH2">
         <v>0.747674441885588</v>
@@ -1214,13 +1214,13 @@
         <v>1.100000023838388</v>
       </c>
       <c r="AJ2">
-        <v>0.8641406624621223</v>
+        <v>0.8641406624621224</v>
       </c>
       <c r="AK2">
-        <v>0.6641535346105982</v>
+        <v>0.6641535346105981</v>
       </c>
       <c r="AL2">
-        <v>2.309012067804556E-13</v>
+        <v>2.281369333681586E-13</v>
       </c>
       <c r="AM2">
         <v>-138.0936484456564</v>
@@ -1229,7 +1229,7 @@
         <v>121.219612890337</v>
       </c>
       <c r="AO2">
-        <v>2.342298947816646E-13</v>
+        <v>2.32796154720776E-13</v>
       </c>
       <c r="AP2">
         <v>-142.8672784204023</v>
@@ -1387,16 +1387,16 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.7630866505842</v>
+        <v>1.763086650584198</v>
       </c>
       <c r="D2">
-        <v>1.7630866505842</v>
+        <v>1.763086650584199</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.7630866505842</v>
+        <v>1.763086650584197</v>
       </c>
       <c r="G2">
         <v>1.763086650584199</v>
@@ -1405,49 +1405,49 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>20.35837104638848</v>
+        <v>20.35837104638846</v>
       </c>
       <c r="J2">
-        <v>20.35837104638847</v>
+        <v>20.35837104638846</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>20.35837104638847</v>
+        <v>20.35837104638844</v>
       </c>
       <c r="M2">
         <v>20.35837104638846</v>
       </c>
       <c r="N2">
-        <v>-7.815970262743036E-15</v>
+        <v>-1.042129368365739E-14</v>
       </c>
       <c r="O2">
-        <v>19.0760556007627</v>
+        <v>19.07605560076268</v>
       </c>
       <c r="P2">
-        <v>-0.3008693307267525</v>
+        <v>-0.3008693307267549</v>
       </c>
       <c r="Q2">
-        <v>2.605323420914346E-15</v>
+        <v>2.605323420914334E-15</v>
       </c>
       <c r="R2">
-        <v>-17.45964880792891</v>
+        <v>-17.45964880792889</v>
       </c>
       <c r="S2">
-        <v>1.91727612356054</v>
+        <v>1.917276123560547</v>
       </c>
       <c r="T2">
-        <v>-3.161100781130179E-29</v>
+        <v>2.605323420914302E-15</v>
       </c>
       <c r="U2">
-        <v>3.991912765039883</v>
+        <v>3.991912765039874</v>
       </c>
       <c r="V2">
-        <v>15.21845990328568</v>
+        <v>15.21845990328567</v>
       </c>
       <c r="W2">
-        <v>1.07931519838309E-29</v>
+        <v>2.605323420914357E-15</v>
       </c>
       <c r="X2">
         <v>-2.15791277681687</v>
@@ -1462,7 +1462,7 @@
         <v>-149.9129785515271</v>
       </c>
       <c r="AB2">
-        <v>30.08702144846559</v>
+        <v>30.08702144846558</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>1.100000023838388</v>
       </c>
       <c r="AG2">
-        <v>0.9573094133256668</v>
+        <v>0.957309413325667</v>
       </c>
       <c r="AH2">
         <v>0.747674441885588</v>
@@ -1486,13 +1486,13 @@
         <v>1.100000023838388</v>
       </c>
       <c r="AJ2">
-        <v>0.8641406624621223</v>
+        <v>0.8641406624621227</v>
       </c>
       <c r="AK2">
-        <v>0.6641535346105981</v>
+        <v>0.6641535346105982</v>
       </c>
       <c r="AL2">
-        <v>2.31727766720924E-13</v>
+        <v>2.403755958133712E-13</v>
       </c>
       <c r="AM2">
         <v>-138.0936484456564</v>
@@ -1501,10 +1501,10 @@
         <v>121.219612890337</v>
       </c>
       <c r="AO2">
-        <v>2.373609554009641E-13</v>
+        <v>2.421140809535288E-13</v>
       </c>
       <c r="AP2">
-        <v>-142.8672784204023</v>
+        <v>-142.8672784204022</v>
       </c>
       <c r="AQ2">
         <v>128.2389811279578</v>
@@ -1659,79 +1659,79 @@
         <v>0</v>
       </c>
       <c r="C2">
+        <v>3.119085825228931</v>
+      </c>
+      <c r="D2">
+        <v>3.119085825228929</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>3.119085825228932</v>
       </c>
-      <c r="D2">
-        <v>3.119085825228932</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>3.119085825228931</v>
-      </c>
       <c r="G2">
-        <v>3.119085825228932</v>
+        <v>3.119085825228929</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
+        <v>36.01610081642939</v>
+      </c>
+      <c r="J2">
+        <v>36.01610081642936</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>36.0161008164294</v>
       </c>
-      <c r="J2">
-        <v>36.0161008164294</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>36.01610081642939</v>
-      </c>
       <c r="M2">
-        <v>36.0161008164294</v>
+        <v>36.01610081642936</v>
       </c>
       <c r="N2">
-        <v>-9.473903143508742E-15</v>
+        <v>4.736951571754547E-15</v>
       </c>
       <c r="O2">
-        <v>26.59966124765507</v>
+        <v>26.59966124765505</v>
       </c>
       <c r="P2">
-        <v>-7.173399904895382</v>
+        <v>-7.173399904895378</v>
       </c>
       <c r="Q2">
-        <v>9.473903143508833E-15</v>
+        <v>-4.736951571754503E-15</v>
       </c>
       <c r="R2">
-        <v>-16.88653057632229</v>
+        <v>-16.88653057632227</v>
       </c>
       <c r="S2">
-        <v>16.88653057622834</v>
+        <v>16.88653057622831</v>
       </c>
       <c r="T2">
-        <v>-9.473903143508922E-15</v>
+        <v>-1.42108547152632E-14</v>
       </c>
       <c r="U2">
-        <v>-0.5158635800632645</v>
+        <v>-0.5158635800632432</v>
       </c>
       <c r="V2">
         <v>11.99572538443091</v>
       </c>
       <c r="W2">
-        <v>9.003101925010973E-29</v>
+        <v>9.473903143508794E-15</v>
       </c>
       <c r="X2">
-        <v>6.255794482090776</v>
+        <v>6.255794482090748</v>
       </c>
       <c r="Y2">
-        <v>-6.255794482403467</v>
+        <v>-6.255794482403457</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-159.6723164477259</v>
+        <v>-159.672316447726</v>
       </c>
       <c r="AB2">
         <v>20.32768355226678</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>20.32768355226679</v>
+        <v>20.32768355226675</v>
       </c>
       <c r="AE2">
         <v>-159.6723164477259</v>
       </c>
       <c r="AF2">
-        <v>1.00000000000431</v>
+        <v>1.000000000004309</v>
       </c>
       <c r="AG2">
-        <v>0.7386880424046126</v>
+        <v>0.7386880424046123</v>
       </c>
       <c r="AH2">
         <v>0.3880750091708057</v>
@@ -1758,13 +1758,13 @@
         <v>1.00000000000431</v>
       </c>
       <c r="AJ2">
-        <v>0.5000000000018684</v>
+        <v>0.5000000000018676</v>
       </c>
       <c r="AK2">
-        <v>0.5000000000024383</v>
+        <v>0.5000000000024378</v>
       </c>
       <c r="AL2">
-        <v>5.427402910044656E-13</v>
+        <v>5.308859298825996E-13</v>
       </c>
       <c r="AM2">
         <v>-160.7833494395999</v>
@@ -1773,7 +1773,7 @@
         <v>141.206952872424</v>
       </c>
       <c r="AO2">
-        <v>5.444849234949683E-13</v>
+        <v>5.133157181881665E-13</v>
       </c>
       <c r="AP2">
         <v>-179.9999999994767</v>
@@ -1931,79 +1931,79 @@
         <v>0</v>
       </c>
       <c r="C2">
+        <v>3.119085825228931</v>
+      </c>
+      <c r="D2">
+        <v>3.119085825228929</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>3.119085825228932</v>
       </c>
-      <c r="D2">
-        <v>3.119085825228932</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>3.119085825228931</v>
-      </c>
       <c r="G2">
-        <v>3.119085825228932</v>
+        <v>3.119085825228929</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
+        <v>36.01610081642939</v>
+      </c>
+      <c r="J2">
+        <v>36.01610081642936</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>36.0161008164294</v>
       </c>
-      <c r="J2">
-        <v>36.0161008164294</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>36.01610081642939</v>
-      </c>
       <c r="M2">
-        <v>36.0161008164294</v>
+        <v>36.01610081642936</v>
       </c>
       <c r="N2">
-        <v>-9.473903143508742E-15</v>
+        <v>4.736951571754547E-15</v>
       </c>
       <c r="O2">
-        <v>26.59966124765507</v>
+        <v>26.59966124765505</v>
       </c>
       <c r="P2">
-        <v>-7.173399904895382</v>
+        <v>-7.173399904895378</v>
       </c>
       <c r="Q2">
-        <v>9.473903143508833E-15</v>
+        <v>-4.736951571754503E-15</v>
       </c>
       <c r="R2">
-        <v>-16.88653057632229</v>
+        <v>-16.88653057632227</v>
       </c>
       <c r="S2">
-        <v>16.88653057622834</v>
+        <v>16.88653057622831</v>
       </c>
       <c r="T2">
-        <v>-9.473903143508922E-15</v>
+        <v>-1.42108547152632E-14</v>
       </c>
       <c r="U2">
-        <v>-0.5158635800632645</v>
+        <v>-0.5158635800632432</v>
       </c>
       <c r="V2">
         <v>11.99572538443091</v>
       </c>
       <c r="W2">
-        <v>9.003101925010973E-29</v>
+        <v>9.473903143508794E-15</v>
       </c>
       <c r="X2">
-        <v>6.255794482090776</v>
+        <v>6.255794482090748</v>
       </c>
       <c r="Y2">
-        <v>-6.255794482403467</v>
+        <v>-6.255794482403457</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-159.6723164477259</v>
+        <v>-159.672316447726</v>
       </c>
       <c r="AB2">
         <v>20.32768355226678</v>
@@ -2012,16 +2012,16 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>20.32768355226679</v>
+        <v>20.32768355226675</v>
       </c>
       <c r="AE2">
         <v>-159.6723164477259</v>
       </c>
       <c r="AF2">
-        <v>1.00000000000431</v>
+        <v>1.000000000004309</v>
       </c>
       <c r="AG2">
-        <v>0.7386880424046126</v>
+        <v>0.7386880424046123</v>
       </c>
       <c r="AH2">
         <v>0.3880750091708057</v>
@@ -2030,13 +2030,13 @@
         <v>1.00000000000431</v>
       </c>
       <c r="AJ2">
-        <v>0.5000000000018684</v>
+        <v>0.5000000000018676</v>
       </c>
       <c r="AK2">
-        <v>0.5000000000024383</v>
+        <v>0.5000000000024378</v>
       </c>
       <c r="AL2">
-        <v>5.427402910044656E-13</v>
+        <v>5.308859298825996E-13</v>
       </c>
       <c r="AM2">
         <v>-160.7833494395999</v>
@@ -2045,7 +2045,7 @@
         <v>141.206952872424</v>
       </c>
       <c r="AO2">
-        <v>5.444849234949683E-13</v>
+        <v>5.133157181881665E-13</v>
       </c>
       <c r="AP2">
         <v>-179.9999999994767</v>
@@ -2206,16 +2206,16 @@
         <v>1.518298438953095</v>
       </c>
       <c r="D2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="G2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -2224,67 +2224,67 @@
         <v>17.53180024879516</v>
       </c>
       <c r="J2">
-        <v>17.53180024879516</v>
+        <v>17.53180024879517</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>17.53180024879516</v>
+        <v>17.53180024879517</v>
       </c>
       <c r="M2">
-        <v>17.53180024879516</v>
+        <v>17.53180024879517</v>
       </c>
       <c r="N2">
-        <v>-5.921189464688818E-16</v>
+        <v>-3.55271367881335E-15</v>
       </c>
       <c r="O2">
         <v>15.39322071800312</v>
       </c>
       <c r="P2">
-        <v>0.7360136868429296</v>
+        <v>0.7360136868429397</v>
       </c>
       <c r="Q2">
-        <v>1.184237892937774E-15</v>
+        <v>3.552713678813361E-15</v>
       </c>
       <c r="R2">
         <v>-13.091678889029</v>
       </c>
       <c r="S2">
-        <v>1.565528142131216</v>
+        <v>1.565528142131208</v>
       </c>
       <c r="T2">
-        <v>-2.36847578587557E-15</v>
+        <v>-1.478679989902205E-29</v>
       </c>
       <c r="U2">
-        <v>2.31352755870836</v>
+        <v>2.313527558708362</v>
       </c>
       <c r="V2">
         <v>11.93279478711934</v>
       </c>
       <c r="W2">
-        <v>2.368475785875572E-15</v>
+        <v>-2.368475785875553E-15</v>
       </c>
       <c r="X2">
-        <v>-0.9534417621250467</v>
+        <v>-0.9534417621250491</v>
       </c>
       <c r="Y2">
-        <v>-10.57270899053605</v>
+        <v>-10.57270899053604</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-146.723813863879</v>
+        <v>-146.7238138638791</v>
       </c>
       <c r="AB2">
-        <v>33.27618613611368</v>
+        <v>33.27618613611372</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>33.27618613611367</v>
+        <v>33.27618613611366</v>
       </c>
       <c r="AE2">
         <v>-146.723813863879</v>
@@ -2293,22 +2293,22 @@
         <v>1.000000000003617</v>
       </c>
       <c r="AG2">
-        <v>0.8878783530243615</v>
+        <v>0.8878783530243616</v>
       </c>
       <c r="AH2">
-        <v>0.681930645912687</v>
+        <v>0.6819306459126868</v>
       </c>
       <c r="AI2">
         <v>1.000000000003617</v>
       </c>
       <c r="AJ2">
-        <v>0.7487167006142579</v>
+        <v>0.7487167006142578</v>
       </c>
       <c r="AK2">
-        <v>0.6096342800273626</v>
+        <v>0.6096342800273622</v>
       </c>
       <c r="AL2">
-        <v>2.413938670134722E-13</v>
+        <v>2.384715750584728E-13</v>
       </c>
       <c r="AM2">
         <v>-138.1765060860386</v>
@@ -2317,10 +2317,10 @@
         <v>119.7466591084986</v>
       </c>
       <c r="AO2">
-        <v>2.360583370850075E-13</v>
+        <v>2.313042975552336E-13</v>
       </c>
       <c r="AP2">
-        <v>-142.5584264979141</v>
+        <v>-142.5584264979142</v>
       </c>
       <c r="AQ2">
         <v>131.6989175372502</v>
@@ -2478,16 +2478,16 @@
         <v>1.518298438953095</v>
       </c>
       <c r="D2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="G2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -2496,67 +2496,67 @@
         <v>17.53180024879516</v>
       </c>
       <c r="J2">
-        <v>17.53180024879516</v>
+        <v>17.53180024879517</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>17.53180024879516</v>
+        <v>17.53180024879517</v>
       </c>
       <c r="M2">
-        <v>17.53180024879516</v>
+        <v>17.53180024879517</v>
       </c>
       <c r="N2">
-        <v>-5.921189464688818E-16</v>
+        <v>-3.55271367881335E-15</v>
       </c>
       <c r="O2">
         <v>15.39322071800312</v>
       </c>
       <c r="P2">
-        <v>0.7360136868429296</v>
+        <v>0.7360136868429397</v>
       </c>
       <c r="Q2">
-        <v>1.184237892937774E-15</v>
+        <v>3.552713678813361E-15</v>
       </c>
       <c r="R2">
         <v>-13.091678889029</v>
       </c>
       <c r="S2">
-        <v>1.565528142131216</v>
+        <v>1.565528142131208</v>
       </c>
       <c r="T2">
-        <v>-2.36847578587557E-15</v>
+        <v>-1.478679989902205E-29</v>
       </c>
       <c r="U2">
-        <v>2.31352755870836</v>
+        <v>2.313527558708362</v>
       </c>
       <c r="V2">
         <v>11.93279478711934</v>
       </c>
       <c r="W2">
-        <v>2.368475785875572E-15</v>
+        <v>-2.368475785875553E-15</v>
       </c>
       <c r="X2">
-        <v>-0.9534417621250467</v>
+        <v>-0.9534417621250491</v>
       </c>
       <c r="Y2">
-        <v>-10.57270899053605</v>
+        <v>-10.57270899053604</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-146.723813863879</v>
+        <v>-146.7238138638791</v>
       </c>
       <c r="AB2">
-        <v>33.27618613611368</v>
+        <v>33.27618613611372</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>33.27618613611367</v>
+        <v>33.27618613611366</v>
       </c>
       <c r="AE2">
         <v>-146.723813863879</v>
@@ -2565,22 +2565,22 @@
         <v>1.000000000003617</v>
       </c>
       <c r="AG2">
-        <v>0.8878783530243615</v>
+        <v>0.8878783530243616</v>
       </c>
       <c r="AH2">
-        <v>0.681930645912687</v>
+        <v>0.6819306459126868</v>
       </c>
       <c r="AI2">
         <v>1.000000000003617</v>
       </c>
       <c r="AJ2">
-        <v>0.7487167006142579</v>
+        <v>0.7487167006142578</v>
       </c>
       <c r="AK2">
-        <v>0.6096342800273626</v>
+        <v>0.6096342800273622</v>
       </c>
       <c r="AL2">
-        <v>2.413938670134722E-13</v>
+        <v>2.384715750584728E-13</v>
       </c>
       <c r="AM2">
         <v>-138.1765060860386</v>
@@ -2589,10 +2589,10 @@
         <v>119.7466591084986</v>
       </c>
       <c r="AO2">
-        <v>2.360583370850075E-13</v>
+        <v>2.313042975552336E-13</v>
       </c>
       <c r="AP2">
-        <v>-142.5584264979141</v>
+        <v>-142.5584264979142</v>
       </c>
       <c r="AQ2">
         <v>131.6989175372502</v>
@@ -2747,16 +2747,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.150115884676078</v>
+        <v>4.150115884676072</v>
       </c>
       <c r="C2">
-        <v>0.001307688437080135</v>
+        <v>0.001307688437079779</v>
       </c>
       <c r="D2">
-        <v>0.001307688437079405</v>
+        <v>0.001307688437080865</v>
       </c>
       <c r="E2">
-        <v>4.149403057445681</v>
+        <v>4.149403057445676</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2765,16 +2765,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>47.92141046371751</v>
+        <v>47.92141046371744</v>
       </c>
       <c r="I2">
-        <v>0.01509988542328754</v>
+        <v>0.01509988542328343</v>
       </c>
       <c r="J2">
-        <v>0.01509988542327911</v>
+        <v>0.01509988542329597</v>
       </c>
       <c r="K2">
-        <v>47.91317944385041</v>
+        <v>47.91317944385035</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2783,49 +2783,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>27.19116803012082</v>
+        <v>27.19116803012081</v>
       </c>
       <c r="O2">
-        <v>0.01384375142257567</v>
+        <v>0.01384375142257197</v>
       </c>
       <c r="P2">
-        <v>-0.01236983620740729</v>
+        <v>-0.01236983620741897</v>
       </c>
       <c r="Q2">
-        <v>3.098069441736109E-10</v>
+        <v>3.097493062399728E-10</v>
       </c>
       <c r="R2">
-        <v>1.230908407987572E-10</v>
+        <v>1.230802098986968E-10</v>
       </c>
       <c r="S2">
-        <v>-1.286645448110905E-08</v>
+        <v>-1.286643884774477E-08</v>
       </c>
       <c r="T2">
-        <v>15.20531856971825</v>
+        <v>15.20531856971822</v>
       </c>
       <c r="U2">
-        <v>0.0003364971267933482</v>
+        <v>0.0003364971267901962</v>
       </c>
       <c r="V2">
-        <v>-0.0115172617250555</v>
+        <v>-0.01151726172507064</v>
       </c>
       <c r="W2">
-        <v>-3.678896776525096E-10</v>
+        <v>-3.679285625499403E-10</v>
       </c>
       <c r="X2">
-        <v>-7.861145318081422E-09</v>
+        <v>-7.861152028485168E-09</v>
       </c>
       <c r="Y2">
-        <v>3.361453364727768E-09</v>
+        <v>3.361453260883005E-09</v>
       </c>
       <c r="Z2">
-        <v>-57.37178929740411</v>
+        <v>-57.37178929740404</v>
       </c>
       <c r="AA2">
-        <v>-114.3324366243354</v>
+        <v>-114.3324366243228</v>
       </c>
       <c r="AB2">
-        <v>-114.3324366243302</v>
+        <v>-114.3324366243407</v>
       </c>
       <c r="AC2">
         <v>122.6433476673685</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6501025958227845</v>
+        <v>0.6501025958227851</v>
       </c>
       <c r="AH2">
-        <v>0.9170824819277787</v>
+        <v>0.9170824819277786</v>
       </c>
       <c r="AI2">
         <v>1.119312077258385</v>
@@ -2849,13 +2849,13 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.8726123019582066</v>
+        <v>0.8726123019582065</v>
       </c>
       <c r="AL2">
-        <v>1.475971874091155</v>
+        <v>1.475971874091154</v>
       </c>
       <c r="AM2">
-        <v>-28.15784081640624</v>
+        <v>-28.15784081640619</v>
       </c>
       <c r="AN2">
         <v>-112.940034452093</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-138.2768647663954</v>
+        <v>-138.2768647663953</v>
       </c>
       <c r="AR2">
         <v>116.1844690690125</v>
@@ -3022,13 +3022,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.150115884676074</v>
+        <v>4.150115884676073</v>
       </c>
       <c r="C2">
-        <v>0.001307688437080015</v>
+        <v>0.001307688437079285</v>
       </c>
       <c r="D2">
-        <v>0.001307688437079743</v>
+        <v>0.001307688437078827</v>
       </c>
       <c r="E2">
         <v>4.149403057445679</v>
@@ -3040,13 +3040,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>47.92141046371747</v>
+        <v>47.92141046371746</v>
       </c>
       <c r="I2">
-        <v>0.01509988542328615</v>
+        <v>0.01509988542327773</v>
       </c>
       <c r="J2">
-        <v>0.01509988542328302</v>
+        <v>0.01509988542327243</v>
       </c>
       <c r="K2">
         <v>47.91317944385037</v>
@@ -3058,52 +3058,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>27.19116803012079</v>
+        <v>27.19116803012081</v>
       </c>
       <c r="O2">
-        <v>0.0138437514225742</v>
+        <v>0.01384375142256652</v>
       </c>
       <c r="P2">
-        <v>-0.0123698362074039</v>
+        <v>-0.01236983620739555</v>
       </c>
       <c r="Q2">
-        <v>3.097928904905736E-10</v>
+        <v>3.097664749099459E-10</v>
       </c>
       <c r="R2">
-        <v>1.230680364311535E-10</v>
+        <v>1.230771247637452E-10</v>
       </c>
       <c r="S2">
-        <v>-1.286644820699438E-08</v>
+        <v>-1.28664545849538E-08</v>
       </c>
       <c r="T2">
-        <v>15.20531856971825</v>
+        <v>15.20531856971822</v>
       </c>
       <c r="U2">
-        <v>0.0003364971268010429</v>
+        <v>0.0003364971267995811</v>
       </c>
       <c r="V2">
-        <v>-0.01151726172506556</v>
+        <v>-0.01151726172505714</v>
       </c>
       <c r="W2">
-        <v>-3.679312132022072E-10</v>
+        <v>-3.679142915612822E-10</v>
       </c>
       <c r="X2">
-        <v>-7.861160114384111E-09</v>
+        <v>-7.861154779475578E-09</v>
       </c>
       <c r="Y2">
-        <v>3.361456449862719E-09</v>
+        <v>3.361437731363485E-09</v>
       </c>
       <c r="Z2">
-        <v>-57.3717892974041</v>
+        <v>-57.37178929740404</v>
       </c>
       <c r="AA2">
-        <v>-114.3324366243674</v>
+        <v>-114.3324366243621</v>
       </c>
       <c r="AB2">
-        <v>-114.3324366243629</v>
+        <v>-114.3324366243613</v>
       </c>
       <c r="AC2">
-        <v>122.6433476673685</v>
+        <v>122.6433476673686</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -3112,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6501025958227846</v>
+        <v>0.6501025958227847</v>
       </c>
       <c r="AH2">
-        <v>0.9170824819277784</v>
+        <v>0.9170824819277789</v>
       </c>
       <c r="AI2">
         <v>1.119312077258385</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.872612301958206</v>
+        <v>0.872612301958207</v>
       </c>
       <c r="AL2">
         <v>1.475971874091154</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-138.2768647663954</v>
+        <v>-138.2768647663953</v>
       </c>
       <c r="AR2">
         <v>116.1844690690125</v>
@@ -3297,13 +3297,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.259987556201642</v>
+        <v>1.259987556201641</v>
       </c>
       <c r="C2">
-        <v>0.0003970181083840191</v>
+        <v>0.0003970181083843986</v>
       </c>
       <c r="D2">
-        <v>0.0003970181083846515</v>
+        <v>0.0003970181083843986</v>
       </c>
       <c r="E2">
         <v>1.259771139729192</v>
@@ -3315,16 +3315,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>14.54908309497194</v>
+        <v>14.54908309497192</v>
       </c>
       <c r="I2">
-        <v>0.00458437023497339</v>
+        <v>0.004584370234977772</v>
       </c>
       <c r="J2">
-        <v>0.004584370234980692</v>
+        <v>0.004584370234977772</v>
       </c>
       <c r="K2">
-        <v>14.54658413279942</v>
+        <v>14.54658413279941</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3333,49 +3333,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>10.4407224534414</v>
+        <v>10.44072245344139</v>
       </c>
       <c r="O2">
-        <v>0.00463909686784625</v>
+        <v>0.004639096867851254</v>
       </c>
       <c r="P2">
-        <v>-0.003769398968301287</v>
+        <v>-0.003769398968300111</v>
       </c>
       <c r="Q2">
-        <v>-7.93511662223036</v>
+        <v>-7.935116622230363</v>
       </c>
       <c r="R2">
-        <v>2.618336765642931E-10</v>
+        <v>2.618358860882063E-10</v>
       </c>
       <c r="S2">
-        <v>-3.125806965576412E-09</v>
+        <v>-3.125804843368527E-09</v>
       </c>
       <c r="T2">
-        <v>9.340123010958143</v>
+        <v>9.340123010958132</v>
       </c>
       <c r="U2">
-        <v>-0.00106327701972714</v>
+        <v>-0.001063277019725668</v>
       </c>
       <c r="V2">
-        <v>-0.003426942863144387</v>
+        <v>-0.003426942863140856</v>
       </c>
       <c r="W2">
-        <v>-7.935116626504438</v>
+        <v>-7.935116626504437</v>
       </c>
       <c r="X2">
-        <v>-2.81991596810224E-09</v>
+        <v>-2.819916027791993E-09</v>
       </c>
       <c r="Y2">
-        <v>1.140571484153015E-09</v>
+        <v>1.140567719566781E-09</v>
       </c>
       <c r="Z2">
-        <v>-48.74026366666284</v>
+        <v>-48.74026366666283</v>
       </c>
       <c r="AA2">
-        <v>-105.7009109935439</v>
+        <v>-105.7009109935746</v>
       </c>
       <c r="AB2">
-        <v>-105.7009109935951</v>
+        <v>-105.7009109935746</v>
       </c>
       <c r="AC2">
         <v>131.2748732981098</v>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9628650605449165</v>
+        <v>0.9628650605449166</v>
       </c>
       <c r="AH2">
         <v>1.038177140583</v>
@@ -3396,7 +3396,7 @@
         <v>1.111241091203317</v>
       </c>
       <c r="AJ2">
-        <v>0.7714491214394115</v>
+        <v>0.7714491214394117</v>
       </c>
       <c r="AK2">
         <v>1.035324491775036</v>
@@ -3405,7 +3405,7 @@
         <v>1.2164108368883</v>
       </c>
       <c r="AM2">
-        <v>-6.924897553952477</v>
+        <v>-6.924897553952476</v>
       </c>
       <c r="AN2">
         <v>-118.6100874847788</v>
@@ -3414,7 +3414,7 @@
         <v>116.5745799757034</v>
       </c>
       <c r="AP2">
-        <v>-3.725126686454219</v>
+        <v>-3.725126686454223</v>
       </c>
       <c r="AQ2">
         <v>-125.2375227398212</v>
@@ -3491,49 +3491,49 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.282962610066691</v>
+        <v>4.282962610066682</v>
       </c>
       <c r="C2">
-        <v>4.282962610066691</v>
+        <v>4.282962610066682</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9.277811204449909</v>
+        <v>9.277811204449897</v>
       </c>
       <c r="F2">
-        <v>148.3661769510664</v>
+        <v>148.3661769510661</v>
       </c>
       <c r="G2">
-        <v>148.3661769510664</v>
+        <v>148.3661769510661</v>
       </c>
       <c r="H2">
-        <v>28.6162797905045</v>
+        <v>28.6162797905042</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>32.46847082824976</v>
+        <v>32.46847082824993</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-77.77984579421403</v>
+        <v>-77.77984579421414</v>
       </c>
       <c r="M2">
-        <v>102.2201542057787</v>
+        <v>102.2201542057786</v>
       </c>
       <c r="N2">
-        <v>0.2917056037382958</v>
+        <v>0.291705603738296</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-29.1713773552606</v>
+        <v>-29.17137735526025</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -3688,13 +3688,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.259987556201641</v>
+        <v>1.259987556201642</v>
       </c>
       <c r="C2">
-        <v>0.0003970181083843693</v>
+        <v>0.0003970181083846099</v>
       </c>
       <c r="D2">
-        <v>0.0003970181083846238</v>
+        <v>0.0003970181083842289</v>
       </c>
       <c r="E2">
         <v>1.259771139729192</v>
@@ -3709,10 +3709,10 @@
         <v>14.54908309497193</v>
       </c>
       <c r="I2">
-        <v>0.004584370234977432</v>
+        <v>0.004584370234980212</v>
       </c>
       <c r="J2">
-        <v>0.004584370234980373</v>
+        <v>0.004584370234975811</v>
       </c>
       <c r="K2">
         <v>14.54658413279941</v>
@@ -3727,49 +3727,49 @@
         <v>10.44072245344139</v>
       </c>
       <c r="O2">
-        <v>0.004639096867851645</v>
+        <v>0.004639096867853707</v>
       </c>
       <c r="P2">
-        <v>-0.003769398968301876</v>
+        <v>-0.00376939896829717</v>
       </c>
       <c r="Q2">
-        <v>-7.935116622230358</v>
+        <v>-7.93511662223036</v>
       </c>
       <c r="R2">
-        <v>2.618332034834742E-10</v>
+        <v>2.618340302656072E-10</v>
       </c>
       <c r="S2">
-        <v>-3.125799116517587E-09</v>
+        <v>-3.125805230884798E-09</v>
       </c>
       <c r="T2">
         <v>9.340123010958136</v>
       </c>
       <c r="U2">
-        <v>-0.001063277019722382</v>
+        <v>-0.001063277019726306</v>
       </c>
       <c r="V2">
-        <v>-0.00342694286314321</v>
+        <v>-0.003426942863140855</v>
       </c>
       <c r="W2">
-        <v>-7.93511662650444</v>
+        <v>-7.935116626504435</v>
       </c>
       <c r="X2">
-        <v>-2.81992088785716E-09</v>
+        <v>-2.819915467395146E-09</v>
       </c>
       <c r="Y2">
-        <v>1.140569294315216E-09</v>
+        <v>1.140562540175291E-09</v>
       </c>
       <c r="Z2">
         <v>-48.74026366666283</v>
       </c>
       <c r="AA2">
-        <v>-105.7009109936142</v>
+        <v>-105.7009109935737</v>
       </c>
       <c r="AB2">
-        <v>-105.7009109935808</v>
+        <v>-105.7009109935968</v>
       </c>
       <c r="AC2">
-        <v>131.2748732981097</v>
+        <v>131.2748732981098</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9628650605449166</v>
+        <v>0.9628650605449164</v>
       </c>
       <c r="AH2">
         <v>1.038177140583</v>
@@ -3787,7 +3787,7 @@
         <v>1.111241091203317</v>
       </c>
       <c r="AJ2">
-        <v>0.7714491214394116</v>
+        <v>0.7714491214394114</v>
       </c>
       <c r="AK2">
         <v>1.035324491775036</v>
@@ -3796,7 +3796,7 @@
         <v>1.2164108368883</v>
       </c>
       <c r="AM2">
-        <v>-6.924897553952477</v>
+        <v>-6.924897553952478</v>
       </c>
       <c r="AN2">
         <v>-118.6100874847788</v>
@@ -3805,7 +3805,7 @@
         <v>116.5745799757034</v>
       </c>
       <c r="AP2">
-        <v>-3.725126686454221</v>
+        <v>-3.725126686454226</v>
       </c>
       <c r="AQ2">
         <v>-125.2375227398212</v>
@@ -3966,13 +3966,13 @@
         <v>2.826503590882589</v>
       </c>
       <c r="C2">
-        <v>0.001514726880395633</v>
+        <v>0.001514726880395903</v>
       </c>
       <c r="D2">
-        <v>0.001514726880396092</v>
+        <v>0.001514726880395291</v>
       </c>
       <c r="E2">
-        <v>2.826014554613983</v>
+        <v>2.826014554613982</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3981,16 +3981,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>32.63765218123014</v>
+        <v>32.63765218123013</v>
       </c>
       <c r="I2">
-        <v>0.01749055944290362</v>
+        <v>0.01749055944290673</v>
       </c>
       <c r="J2">
-        <v>0.01749055944290891</v>
+        <v>0.01749055944289967</v>
       </c>
       <c r="K2">
-        <v>32.63200527680367</v>
+        <v>32.63200527680366</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4002,49 +4002,49 @@
         <v>24.21629159096679</v>
       </c>
       <c r="O2">
-        <v>0.01474207751742153</v>
+        <v>0.01474207751742317</v>
       </c>
       <c r="P2">
-        <v>-0.01341928711892547</v>
+        <v>-0.01341928711891664</v>
       </c>
       <c r="Q2">
-        <v>-9.783236161103701E-11</v>
+        <v>-9.784020569240743E-11</v>
       </c>
       <c r="R2">
-        <v>-4.308160915823539E-09</v>
+        <v>-4.308160485934143E-09</v>
       </c>
       <c r="S2">
-        <v>-1.647189948667565E-08</v>
+        <v>-1.647190842419032E-08</v>
       </c>
       <c r="T2">
-        <v>7.041002540869041</v>
+        <v>7.04100254086907</v>
       </c>
       <c r="U2">
-        <v>-0.001500030071429446</v>
+        <v>-0.001500030071439345</v>
       </c>
       <c r="V2">
-        <v>-0.01266679104744409</v>
+        <v>-0.01266679104743923</v>
       </c>
       <c r="W2">
-        <v>1.239701506895669E-11</v>
+        <v>1.238387922749811E-11</v>
       </c>
       <c r="X2">
-        <v>-1.028676757525728E-08</v>
+        <v>-1.028675949509931E-08</v>
       </c>
       <c r="Y2">
-        <v>6.073137106373835E-09</v>
+        <v>6.073124945582538E-09</v>
       </c>
       <c r="Z2">
-        <v>-40.47982361172813</v>
+        <v>-40.47982361172819</v>
       </c>
       <c r="AA2">
-        <v>-111.6296970855612</v>
+        <v>-111.6296970855238</v>
       </c>
       <c r="AB2">
-        <v>-111.6296970855418</v>
+        <v>-111.6296970855497</v>
       </c>
       <c r="AC2">
-        <v>139.5492395016656</v>
+        <v>139.5492395016655</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4053,10 +4053,10 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.772700481295814</v>
+        <v>0.7727004812958143</v>
       </c>
       <c r="AH2">
-        <v>0.8472111075846838</v>
+        <v>0.8472111075846839</v>
       </c>
       <c r="AI2">
         <v>1.055044340439988</v>
@@ -4065,13 +4065,13 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.9475300844110901</v>
+        <v>0.94753008441109</v>
       </c>
       <c r="AL2">
         <v>1.491564952024011</v>
       </c>
       <c r="AM2">
-        <v>-24.26778175483754</v>
+        <v>-24.26778175483753</v>
       </c>
       <c r="AN2">
         <v>-117.4396388970154</v>
@@ -4241,13 +4241,13 @@
         <v>2.826503590882589</v>
       </c>
       <c r="C2">
-        <v>0.001514726880395633</v>
+        <v>0.001514726880395903</v>
       </c>
       <c r="D2">
-        <v>0.001514726880396092</v>
+        <v>0.001514726880395291</v>
       </c>
       <c r="E2">
-        <v>2.826014554613983</v>
+        <v>2.826014554613982</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4256,16 +4256,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>32.63765218123014</v>
+        <v>32.63765218123013</v>
       </c>
       <c r="I2">
-        <v>0.01749055944290362</v>
+        <v>0.01749055944290673</v>
       </c>
       <c r="J2">
-        <v>0.01749055944290891</v>
+        <v>0.01749055944289967</v>
       </c>
       <c r="K2">
-        <v>32.63200527680367</v>
+        <v>32.63200527680366</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4277,49 +4277,49 @@
         <v>24.21629159096679</v>
       </c>
       <c r="O2">
-        <v>0.01474207751742153</v>
+        <v>0.01474207751742317</v>
       </c>
       <c r="P2">
-        <v>-0.01341928711892547</v>
+        <v>-0.01341928711891664</v>
       </c>
       <c r="Q2">
-        <v>-9.783236161103701E-11</v>
+        <v>-9.784020569240743E-11</v>
       </c>
       <c r="R2">
-        <v>-4.308160915823539E-09</v>
+        <v>-4.308160485934143E-09</v>
       </c>
       <c r="S2">
-        <v>-1.647189948667565E-08</v>
+        <v>-1.647190842419032E-08</v>
       </c>
       <c r="T2">
-        <v>7.041002540869041</v>
+        <v>7.04100254086907</v>
       </c>
       <c r="U2">
-        <v>-0.001500030071429446</v>
+        <v>-0.001500030071439345</v>
       </c>
       <c r="V2">
-        <v>-0.01266679104744409</v>
+        <v>-0.01266679104743923</v>
       </c>
       <c r="W2">
-        <v>1.239701506895669E-11</v>
+        <v>1.238387922749811E-11</v>
       </c>
       <c r="X2">
-        <v>-1.028676757525728E-08</v>
+        <v>-1.028675949509931E-08</v>
       </c>
       <c r="Y2">
-        <v>6.073137106373835E-09</v>
+        <v>6.073124945582538E-09</v>
       </c>
       <c r="Z2">
-        <v>-40.47982361172813</v>
+        <v>-40.47982361172819</v>
       </c>
       <c r="AA2">
-        <v>-111.6296970855612</v>
+        <v>-111.6296970855238</v>
       </c>
       <c r="AB2">
-        <v>-111.6296970855418</v>
+        <v>-111.6296970855497</v>
       </c>
       <c r="AC2">
-        <v>139.5492395016656</v>
+        <v>139.5492395016655</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4328,10 +4328,10 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.772700481295814</v>
+        <v>0.7727004812958143</v>
       </c>
       <c r="AH2">
-        <v>0.8472111075846838</v>
+        <v>0.8472111075846839</v>
       </c>
       <c r="AI2">
         <v>1.055044340439988</v>
@@ -4340,13 +4340,13 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.9475300844110901</v>
+        <v>0.94753008441109</v>
       </c>
       <c r="AL2">
         <v>1.491564952024011</v>
       </c>
       <c r="AM2">
-        <v>-24.26778175483754</v>
+        <v>-24.26778175483753</v>
       </c>
       <c r="AN2">
         <v>-117.4396388970154</v>
@@ -4516,10 +4516,10 @@
         <v>1.035889633734118</v>
       </c>
       <c r="C2">
-        <v>0.0005551345763019209</v>
+        <v>0.0005551345763020945</v>
       </c>
       <c r="D2">
-        <v>0.0005551345763020886</v>
+        <v>0.0005551345763017319</v>
       </c>
       <c r="E2">
         <v>1.035710406082399</v>
@@ -4534,10 +4534,10 @@
         <v>11.96142317774272</v>
       </c>
       <c r="I2">
-        <v>0.006410141941287657</v>
+        <v>0.006410141941289662</v>
       </c>
       <c r="J2">
-        <v>0.006410141941289594</v>
+        <v>0.006410141941285475</v>
       </c>
       <c r="K2">
         <v>11.9593536350834</v>
@@ -4552,46 +4552,46 @@
         <v>8.614323075904126</v>
       </c>
       <c r="O2">
-        <v>0.006036631569588619</v>
+        <v>0.006036631569590199</v>
       </c>
       <c r="P2">
-        <v>-0.004065327085945807</v>
+        <v>-0.004065327085945831</v>
       </c>
       <c r="Q2">
-        <v>-5.363480227314727</v>
+        <v>-5.363480227314728</v>
       </c>
       <c r="R2">
-        <v>-4.817259473514814E-11</v>
+        <v>-4.817590971188532E-11</v>
       </c>
       <c r="S2">
-        <v>-4.802054527571103E-09</v>
+        <v>-4.802055719663172E-09</v>
       </c>
       <c r="T2">
         <v>6.312848364667325</v>
       </c>
       <c r="U2">
-        <v>-0.0004724106998726073</v>
+        <v>-0.0004724106998766798</v>
       </c>
       <c r="V2">
-        <v>-0.005078948493513015</v>
+        <v>-0.00507894849350764</v>
       </c>
       <c r="W2">
-        <v>-5.363480230218024</v>
+        <v>-5.363480230218023</v>
       </c>
       <c r="X2">
-        <v>-4.065632728802221E-09</v>
+        <v>-4.065626274853441E-09</v>
       </c>
       <c r="Y2">
-        <v>1.698287460998309E-09</v>
+        <v>1.698278586940711E-09</v>
       </c>
       <c r="Z2">
         <v>-43.36332196693331</v>
       </c>
       <c r="AA2">
-        <v>-114.5131954407511</v>
+        <v>-114.5131954407139</v>
       </c>
       <c r="AB2">
-        <v>-114.5131954407636</v>
+        <v>-114.5131954407338</v>
       </c>
       <c r="AC2">
         <v>136.6657411464604</v>
@@ -4603,10 +4603,10 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8928555332546843</v>
+        <v>0.8928555332546844</v>
       </c>
       <c r="AH2">
-        <v>0.9446106203901294</v>
+        <v>0.9446106203901293</v>
       </c>
       <c r="AI2">
         <v>1.014888974463672</v>
@@ -4615,13 +4615,13 @@
         <v>0.6342405043354559</v>
       </c>
       <c r="AK2">
-        <v>0.9425752860361225</v>
+        <v>0.9425752860361224</v>
       </c>
       <c r="AL2">
         <v>1.180796373306989</v>
       </c>
       <c r="AM2">
-        <v>-7.12818181849163</v>
+        <v>-7.128181818491637</v>
       </c>
       <c r="AN2">
         <v>-118.9878906721926</v>
@@ -4630,7 +4630,7 @@
         <v>116.8120844345216</v>
       </c>
       <c r="AP2">
-        <v>1.665741161973212</v>
+        <v>1.665741161973207</v>
       </c>
       <c r="AQ2">
         <v>-130.1934967078016</v>
@@ -4791,10 +4791,10 @@
         <v>1.035889633734118</v>
       </c>
       <c r="C2">
-        <v>0.0005551345763019209</v>
+        <v>0.0005551345763020945</v>
       </c>
       <c r="D2">
-        <v>0.0005551345763020886</v>
+        <v>0.0005551345763017319</v>
       </c>
       <c r="E2">
         <v>1.035710406082399</v>
@@ -4809,10 +4809,10 @@
         <v>11.96142317774272</v>
       </c>
       <c r="I2">
-        <v>0.006410141941287657</v>
+        <v>0.006410141941289662</v>
       </c>
       <c r="J2">
-        <v>0.006410141941289594</v>
+        <v>0.006410141941285475</v>
       </c>
       <c r="K2">
         <v>11.9593536350834</v>
@@ -4827,46 +4827,46 @@
         <v>8.614323075904126</v>
       </c>
       <c r="O2">
-        <v>0.006036631569588619</v>
+        <v>0.006036631569590199</v>
       </c>
       <c r="P2">
-        <v>-0.004065327085945807</v>
+        <v>-0.004065327085945831</v>
       </c>
       <c r="Q2">
-        <v>-5.363480227314727</v>
+        <v>-5.363480227314728</v>
       </c>
       <c r="R2">
-        <v>-4.817259473514814E-11</v>
+        <v>-4.817590971188532E-11</v>
       </c>
       <c r="S2">
-        <v>-4.802054527571103E-09</v>
+        <v>-4.802055719663172E-09</v>
       </c>
       <c r="T2">
         <v>6.312848364667325</v>
       </c>
       <c r="U2">
-        <v>-0.0004724106998726073</v>
+        <v>-0.0004724106998766798</v>
       </c>
       <c r="V2">
-        <v>-0.005078948493513015</v>
+        <v>-0.00507894849350764</v>
       </c>
       <c r="W2">
-        <v>-5.363480230218024</v>
+        <v>-5.363480230218023</v>
       </c>
       <c r="X2">
-        <v>-4.065632728802221E-09</v>
+        <v>-4.065626274853441E-09</v>
       </c>
       <c r="Y2">
-        <v>1.698287460998309E-09</v>
+        <v>1.698278586940711E-09</v>
       </c>
       <c r="Z2">
         <v>-43.36332196693331</v>
       </c>
       <c r="AA2">
-        <v>-114.5131954407511</v>
+        <v>-114.5131954407139</v>
       </c>
       <c r="AB2">
-        <v>-114.5131954407636</v>
+        <v>-114.5131954407338</v>
       </c>
       <c r="AC2">
         <v>136.6657411464604</v>
@@ -4878,10 +4878,10 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8928555332546843</v>
+        <v>0.8928555332546844</v>
       </c>
       <c r="AH2">
-        <v>0.9446106203901294</v>
+        <v>0.9446106203901293</v>
       </c>
       <c r="AI2">
         <v>1.014888974463672</v>
@@ -4890,13 +4890,13 @@
         <v>0.6342405043354559</v>
       </c>
       <c r="AK2">
-        <v>0.9425752860361225</v>
+        <v>0.9425752860361224</v>
       </c>
       <c r="AL2">
         <v>1.180796373306989</v>
       </c>
       <c r="AM2">
-        <v>-7.12818181849163</v>
+        <v>-7.128181818491637</v>
       </c>
       <c r="AN2">
         <v>-118.9878906721926</v>
@@ -4905,7 +4905,7 @@
         <v>116.8120844345216</v>
       </c>
       <c r="AP2">
-        <v>1.665741161973212</v>
+        <v>1.665741161973207</v>
       </c>
       <c r="AQ2">
         <v>-130.1934967078016</v>
@@ -5063,100 +5063,100 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.001143871084790616</v>
+        <v>0.001143871084791481</v>
       </c>
       <c r="C2">
-        <v>5.026871232902586</v>
+        <v>5.026871232902589</v>
       </c>
       <c r="D2">
-        <v>2.972832707499776</v>
+        <v>2.97283270749978</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>5.026925725199457</v>
+        <v>5.026925725199461</v>
       </c>
       <c r="G2">
-        <v>2.971978874847182</v>
+        <v>2.971978874847185</v>
       </c>
       <c r="H2">
-        <v>0.01320828557444182</v>
+        <v>0.01320828557445181</v>
       </c>
       <c r="I2">
-        <v>58.04530918995788</v>
+        <v>58.04530918995791</v>
       </c>
       <c r="J2">
-        <v>34.3273152786144</v>
+        <v>34.32731527861444</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>58.04593841280323</v>
+        <v>58.04593841280327</v>
       </c>
       <c r="M2">
-        <v>34.31745606837804</v>
+        <v>34.31745606837807</v>
       </c>
       <c r="N2">
-        <v>-0.0002505500822239035</v>
+        <v>-0.0002505500822206526</v>
       </c>
       <c r="O2">
-        <v>31.94042916440141</v>
+        <v>31.94042916440144</v>
       </c>
       <c r="P2">
-        <v>-0.2508696004404089</v>
+        <v>-0.2508696004403994</v>
       </c>
       <c r="Q2">
-        <v>-9.750546482709596E-09</v>
+        <v>-9.750573447419375E-09</v>
       </c>
       <c r="R2">
-        <v>2.355193261539687E-10</v>
+        <v>2.355114192600326E-10</v>
       </c>
       <c r="S2">
-        <v>1.560736596583783E-10</v>
+        <v>1.560604009357315E-10</v>
       </c>
       <c r="T2">
-        <v>-0.01290413886790816</v>
+        <v>-0.01290413886791798</v>
       </c>
       <c r="U2">
-        <v>7.953445881180607</v>
+        <v>7.953445881180589</v>
       </c>
       <c r="V2">
-        <v>16.03313910681054</v>
+        <v>16.03313910681056</v>
       </c>
       <c r="W2">
-        <v>-3.442933648091712E-09</v>
+        <v>-3.442940391165594E-09</v>
       </c>
       <c r="X2">
-        <v>-1.520485249207433E-10</v>
+        <v>-1.520297423987108E-10</v>
       </c>
       <c r="Y2">
-        <v>-5.239738173560941E-11</v>
+        <v>-5.240097560117468E-11</v>
       </c>
       <c r="Z2">
-        <v>82.86821583349334</v>
+        <v>82.86821583347806</v>
       </c>
       <c r="AA2">
-        <v>175.5922528769732</v>
+        <v>175.5922528769733</v>
       </c>
       <c r="AB2">
-        <v>41.15861451898611</v>
+        <v>41.15861451898609</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>-4.394724263667674</v>
+        <v>-4.394724263667634</v>
       </c>
       <c r="AE2">
         <v>-138.8560581155532</v>
       </c>
       <c r="AG2">
-        <v>0.9771571744427108</v>
+        <v>0.9771571744427107</v>
       </c>
       <c r="AH2">
-        <v>0.5670703897403271</v>
+        <v>0.5670703897403272</v>
       </c>
       <c r="AI2">
         <v>0.4671236747649691</v>
@@ -5171,7 +5171,7 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-8.244114005996616</v>
+        <v>-8.244114005996629</v>
       </c>
       <c r="AN2">
         <v>-170.4249704778445</v>
@@ -5338,7 +5338,7 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.001143871084790565</v>
+        <v>0.001143871084790514</v>
       </c>
       <c r="C2">
         <v>5.02687123290259</v>
@@ -5350,91 +5350,91 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>5.026925725199461</v>
+        <v>5.026925725199462</v>
       </c>
       <c r="G2">
         <v>2.971978874847186</v>
       </c>
       <c r="H2">
-        <v>0.01320828557444124</v>
+        <v>0.01320828557444065</v>
       </c>
       <c r="I2">
         <v>58.04530918995793</v>
       </c>
       <c r="J2">
-        <v>34.32731527861442</v>
+        <v>34.32731527861441</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>58.04593841280327</v>
+        <v>58.04593841280328</v>
       </c>
       <c r="M2">
-        <v>34.31745606837809</v>
+        <v>34.31745606837808</v>
       </c>
       <c r="N2">
-        <v>-0.000250550082228484</v>
+        <v>-0.0002505500822330643</v>
       </c>
       <c r="O2">
         <v>31.94042916440146</v>
       </c>
       <c r="P2">
-        <v>-0.2508696004403994</v>
+        <v>-0.2508696004404053</v>
       </c>
       <c r="Q2">
-        <v>-9.750564008633093E-09</v>
+        <v>-9.750537043923311E-09</v>
       </c>
       <c r="R2">
-        <v>2.355178447060359E-10</v>
+        <v>2.355242701520394E-10</v>
       </c>
       <c r="S2">
-        <v>1.560625453843186E-10</v>
+        <v>1.560500113701607E-10</v>
       </c>
       <c r="T2">
-        <v>-0.0129041388679075</v>
+        <v>-0.01290413886790683</v>
       </c>
       <c r="U2">
-        <v>7.953445881180591</v>
+        <v>7.953445881180611</v>
       </c>
       <c r="V2">
-        <v>16.03313910681055</v>
+        <v>16.03313910681056</v>
       </c>
       <c r="W2">
-        <v>-3.44295522137669E-09</v>
+        <v>-3.442948478302809E-09</v>
       </c>
       <c r="X2">
-        <v>-1.520292485827334E-10</v>
+        <v>-1.520287547667558E-10</v>
       </c>
       <c r="Y2">
-        <v>-5.239273048419105E-11</v>
+        <v>-5.240707626957153E-11</v>
       </c>
       <c r="Z2">
-        <v>82.86821583351373</v>
+        <v>82.86821583353412</v>
       </c>
       <c r="AA2">
         <v>175.5922528769733</v>
       </c>
       <c r="AB2">
-        <v>41.15861451898613</v>
+        <v>41.15861451898609</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>-4.394724263667615</v>
+        <v>-4.394724263667604</v>
       </c>
       <c r="AE2">
-        <v>-138.8560581155531</v>
+        <v>-138.8560581155532</v>
       </c>
       <c r="AG2">
         <v>0.977157174442711</v>
       </c>
       <c r="AH2">
-        <v>0.5670703897403273</v>
+        <v>0.5670703897403275</v>
       </c>
       <c r="AI2">
-        <v>0.4671236747649692</v>
+        <v>0.4671236747649695</v>
       </c>
       <c r="AJ2">
         <v>1.312059302960689</v>
@@ -5446,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-8.244114005996614</v>
+        <v>-8.244114005996613</v>
       </c>
       <c r="AN2">
         <v>-170.4249704778445</v>
@@ -5455,7 +5455,7 @@
         <v>132.0550451157561</v>
       </c>
       <c r="AP2">
-        <v>-12.52501517682081</v>
+        <v>-12.52501517682079</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -5619,13 +5619,13 @@
         <v>1.382386873692203</v>
       </c>
       <c r="D2">
-        <v>1.177072767658897</v>
+        <v>1.177072767658898</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.382520063691103</v>
+        <v>1.382520063691104</v>
       </c>
       <c r="G2">
         <v>1.176705138606269</v>
@@ -5634,55 +5634,55 @@
         <v>0.004376191795301171</v>
       </c>
       <c r="I2">
-        <v>15.96242867300798</v>
+        <v>15.96242867300797</v>
       </c>
       <c r="J2">
-        <v>13.59166558527284</v>
+        <v>13.59166558527285</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>15.96396661864234</v>
+        <v>15.96396661864235</v>
       </c>
       <c r="M2">
         <v>13.58742057062291</v>
       </c>
       <c r="N2">
-        <v>0.0006412014006273041</v>
+        <v>0.000641201400627304</v>
       </c>
       <c r="O2">
-        <v>11.98351855411372</v>
+        <v>11.98351855411371</v>
       </c>
       <c r="P2">
-        <v>7.741742056906001</v>
+        <v>7.741742056906009</v>
       </c>
       <c r="Q2">
-        <v>-2.609766867608111E-09</v>
+        <v>-2.60976960198721E-09</v>
       </c>
       <c r="R2">
-        <v>-9.55680863293294</v>
+        <v>-9.556808632932944</v>
       </c>
       <c r="S2">
-        <v>-6.92317491373013</v>
+        <v>-6.923174913730129</v>
       </c>
       <c r="T2">
         <v>-0.00456910216784159</v>
       </c>
       <c r="U2">
-        <v>9.557683331464967</v>
+        <v>9.557683331464965</v>
       </c>
       <c r="V2">
-        <v>9.294480388845983</v>
+        <v>9.29448038884599</v>
       </c>
       <c r="W2">
-        <v>-1.530295250907789E-09</v>
+        <v>-1.530295019955643E-09</v>
       </c>
       <c r="X2">
-        <v>-9.556808635331517</v>
+        <v>-9.556808635331524</v>
       </c>
       <c r="Y2">
-        <v>-6.923174919701171</v>
+        <v>-6.923174919701172</v>
       </c>
       <c r="Z2">
         <v>79.62743609719017</v>
@@ -5697,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>10.20990687633835</v>
+        <v>10.20990687633836</v>
       </c>
       <c r="AE2">
         <v>-114.438849573896</v>
@@ -5706,16 +5706,16 @@
         <v>1.054312579845774</v>
       </c>
       <c r="AH2">
-        <v>0.96026804586595</v>
+        <v>0.9602680458659502</v>
       </c>
       <c r="AI2">
-        <v>0.8899836711803117</v>
+        <v>0.8899836711803119</v>
       </c>
       <c r="AJ2">
         <v>1.158599621240366</v>
       </c>
       <c r="AK2">
-        <v>0.8466171789416777</v>
+        <v>0.8466171789416779</v>
       </c>
       <c r="AL2">
         <v>0.7205817918869085</v>
@@ -5730,7 +5730,7 @@
         <v>115.7733745763009</v>
       </c>
       <c r="AP2">
-        <v>-4.827878725560209</v>
+        <v>-4.827878725560213</v>
       </c>
       <c r="AQ2">
         <v>-124.7900931164661</v>
@@ -5888,13 +5888,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003789893266568064</v>
+        <v>0.0003789893266563844</v>
       </c>
       <c r="C2">
         <v>1.382386873692203</v>
       </c>
       <c r="D2">
-        <v>1.177072767658897</v>
+        <v>1.177072767658896</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5903,16 +5903,16 @@
         <v>1.382520063691104</v>
       </c>
       <c r="G2">
-        <v>1.176705138606269</v>
+        <v>1.176705138606268</v>
       </c>
       <c r="H2">
-        <v>0.004376191795306044</v>
+        <v>0.004376191795301171</v>
       </c>
       <c r="I2">
-        <v>15.96242867300798</v>
+        <v>15.96242867300797</v>
       </c>
       <c r="J2">
-        <v>13.59166558527284</v>
+        <v>13.59166558527283</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -5921,46 +5921,46 @@
         <v>15.96396661864235</v>
       </c>
       <c r="M2">
-        <v>13.58742057062291</v>
+        <v>13.5874205706229</v>
       </c>
       <c r="N2">
-        <v>0.0006412014006283442</v>
+        <v>0.0006412014006273044</v>
       </c>
       <c r="O2">
         <v>11.98351855411372</v>
       </c>
       <c r="P2">
-        <v>7.741742056905998</v>
+        <v>7.741742056905991</v>
       </c>
       <c r="Q2">
-        <v>-2.609769371035063E-09</v>
+        <v>-2.609766636655964E-09</v>
       </c>
       <c r="R2">
-        <v>-9.556808632932944</v>
+        <v>-9.556808632932949</v>
       </c>
       <c r="S2">
-        <v>-6.923174913730126</v>
+        <v>-6.923174913730128</v>
       </c>
       <c r="T2">
-        <v>-0.004569102167846633</v>
+        <v>-0.00456910216784159</v>
       </c>
       <c r="U2">
         <v>9.557683331464965</v>
       </c>
       <c r="V2">
-        <v>9.294480388845988</v>
+        <v>9.294480388845978</v>
       </c>
       <c r="W2">
-        <v>-1.530292285576545E-09</v>
+        <v>-1.530292516528691E-09</v>
       </c>
       <c r="X2">
-        <v>-9.556808635331521</v>
+        <v>-9.556808635331517</v>
       </c>
       <c r="Y2">
-        <v>-6.923174919701172</v>
+        <v>-6.923174919701166</v>
       </c>
       <c r="Z2">
-        <v>79.62743609718609</v>
+        <v>79.62743609719017</v>
       </c>
       <c r="AA2">
         <v>-169.8047984139787</v>
@@ -5972,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>10.20990687633837</v>
+        <v>10.2099068763384</v>
       </c>
       <c r="AE2">
         <v>-114.438849573896</v>
@@ -5981,22 +5981,22 @@
         <v>1.054312579845774</v>
       </c>
       <c r="AH2">
-        <v>0.9602680458659499</v>
+        <v>0.9602680458659503</v>
       </c>
       <c r="AI2">
-        <v>0.8899836711803117</v>
+        <v>0.8899836711803119</v>
       </c>
       <c r="AJ2">
         <v>1.158599621240366</v>
       </c>
       <c r="AK2">
-        <v>0.8466171789416778</v>
+        <v>0.846617178941678</v>
       </c>
       <c r="AL2">
-        <v>0.7205817918869084</v>
+        <v>0.7205817918869087</v>
       </c>
       <c r="AM2">
-        <v>-2.384172943571883</v>
+        <v>-2.384172943571882</v>
       </c>
       <c r="AN2">
         <v>-131.2300202118273</v>
@@ -6005,7 +6005,7 @@
         <v>115.7733745763009</v>
       </c>
       <c r="AP2">
-        <v>-4.827878725560208</v>
+        <v>-4.827878725560205</v>
       </c>
       <c r="AQ2">
         <v>-124.7900931164661</v>
@@ -6163,7 +6163,7 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.001105760050859194</v>
+        <v>0.001105760050857464</v>
       </c>
       <c r="C2">
         <v>3.92133157943606</v>
@@ -6181,7 +6181,7 @@
         <v>2.491243992186031</v>
       </c>
       <c r="H2">
-        <v>0.0127682172604538</v>
+        <v>0.01276821726043383</v>
       </c>
       <c r="I2">
         <v>45.2796368593838</v>
@@ -6196,73 +6196,73 @@
         <v>45.28295866003549</v>
       </c>
       <c r="M2">
-        <v>28.76640779011286</v>
+        <v>28.76640779011285</v>
       </c>
       <c r="N2">
-        <v>-0.0001657433366640072</v>
+        <v>-0.0001657433366732765</v>
       </c>
       <c r="O2">
         <v>30.315630938095</v>
       </c>
       <c r="P2">
-        <v>-0.1080137594025399</v>
+        <v>-0.1080137594025518</v>
       </c>
       <c r="Q2">
-        <v>-1.107386978157234E-08</v>
+        <v>-1.10738665286572E-08</v>
       </c>
       <c r="R2">
-        <v>-1.701665039681249E-10</v>
+        <v>-1.701697660904987E-10</v>
       </c>
       <c r="S2">
-        <v>-2.613670108264897E-11</v>
+        <v>-2.613156653520519E-11</v>
       </c>
       <c r="T2">
-        <v>-0.01215427121316831</v>
+        <v>-0.01215427121314916</v>
       </c>
       <c r="U2">
-        <v>1.849625463043422</v>
+        <v>1.849625463043413</v>
       </c>
       <c r="V2">
-        <v>12.13153436196902</v>
+        <v>12.131534361969</v>
       </c>
       <c r="W2">
-        <v>-2.245472926049091E-09</v>
+        <v>-2.245492354581442E-09</v>
       </c>
       <c r="X2">
-        <v>-1.937148288569783E-10</v>
+        <v>-1.937040709188358E-10</v>
       </c>
       <c r="Y2">
-        <v>-1.618471938001772E-10</v>
+        <v>-1.618430724436743E-10</v>
       </c>
       <c r="Z2">
-        <v>84.60871947156714</v>
+        <v>84.60871947161206</v>
       </c>
       <c r="AA2">
         <v>-170.3193910162658</v>
       </c>
       <c r="AB2">
-        <v>37.22943985112055</v>
+        <v>37.22943985112049</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>9.696208662707562</v>
+        <v>9.696208662707537</v>
       </c>
       <c r="AE2">
         <v>-142.7892737871882</v>
       </c>
       <c r="AG2">
-        <v>0.9520045753620061</v>
+        <v>0.9520045753620058</v>
       </c>
       <c r="AH2">
-        <v>0.6707651729559317</v>
+        <v>0.6707651729559316</v>
       </c>
       <c r="AI2">
-        <v>0.4216157504340802</v>
+        <v>0.4216157504340798</v>
       </c>
       <c r="AJ2">
-        <v>1.315056832745735</v>
+        <v>1.315056832745734</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -6271,13 +6271,13 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-6.172553624091376</v>
+        <v>-6.172553624091377</v>
       </c>
       <c r="AN2">
         <v>-166.827973412876</v>
       </c>
       <c r="AO2">
-        <v>127.7395623824123</v>
+        <v>127.7395623824122</v>
       </c>
       <c r="AP2">
         <v>-8.930089734159868</v>
@@ -6357,52 +6357,52 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.309686024628783</v>
+        <v>1.309686024628784</v>
       </c>
       <c r="C2">
-        <v>1.309686024628783</v>
+        <v>1.309686024628784</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2.837059479583175</v>
+        <v>2.837059479583173</v>
       </c>
       <c r="F2">
-        <v>45.36885473239913</v>
+        <v>45.36885473239914</v>
       </c>
       <c r="G2">
-        <v>45.36885473239913</v>
+        <v>45.36885473239914</v>
       </c>
       <c r="H2">
-        <v>28.40499517047036</v>
+        <v>28.40499517047038</v>
       </c>
       <c r="I2">
-        <v>-25.72916224161305</v>
+        <v>-25.72916224161306</v>
       </c>
       <c r="J2">
         <v>28.76520341755293</v>
       </c>
       <c r="K2">
-        <v>-25.72916225404876</v>
+        <v>-25.72916225404875</v>
       </c>
       <c r="L2">
-        <v>-54.52967391402494</v>
+        <v>-54.52967391402492</v>
       </c>
       <c r="M2">
         <v>125.4703260859678</v>
       </c>
       <c r="N2">
-        <v>0.8910570420386135</v>
+        <v>0.8910570420386132</v>
       </c>
       <c r="O2">
-        <v>0.8020156209364414</v>
+        <v>0.802015620936441</v>
       </c>
       <c r="P2">
-        <v>-9.168679204911147</v>
+        <v>-9.16867920491114</v>
       </c>
       <c r="Q2">
-        <v>-9.529673900180349</v>
+        <v>-9.529673900180343</v>
       </c>
     </row>
   </sheetData>
@@ -6554,7 +6554,7 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.001105760050859194</v>
+        <v>0.001105760050857464</v>
       </c>
       <c r="C2">
         <v>3.92133157943606</v>
@@ -6572,7 +6572,7 @@
         <v>2.491243992186031</v>
       </c>
       <c r="H2">
-        <v>0.0127682172604538</v>
+        <v>0.01276821726043383</v>
       </c>
       <c r="I2">
         <v>45.2796368593838</v>
@@ -6587,73 +6587,73 @@
         <v>45.28295866003549</v>
       </c>
       <c r="M2">
-        <v>28.76640779011286</v>
+        <v>28.76640779011285</v>
       </c>
       <c r="N2">
-        <v>-0.0001657433366640072</v>
+        <v>-0.0001657433366732765</v>
       </c>
       <c r="O2">
         <v>30.315630938095</v>
       </c>
       <c r="P2">
-        <v>-0.1080137594025399</v>
+        <v>-0.1080137594025518</v>
       </c>
       <c r="Q2">
-        <v>-1.107386978157234E-08</v>
+        <v>-1.10738665286572E-08</v>
       </c>
       <c r="R2">
-        <v>-1.701665039681249E-10</v>
+        <v>-1.701697660904987E-10</v>
       </c>
       <c r="S2">
-        <v>-2.613670108264897E-11</v>
+        <v>-2.613156653520519E-11</v>
       </c>
       <c r="T2">
-        <v>-0.01215427121316831</v>
+        <v>-0.01215427121314916</v>
       </c>
       <c r="U2">
-        <v>1.849625463043422</v>
+        <v>1.849625463043413</v>
       </c>
       <c r="V2">
-        <v>12.13153436196902</v>
+        <v>12.131534361969</v>
       </c>
       <c r="W2">
-        <v>-2.245472926049091E-09</v>
+        <v>-2.245492354581442E-09</v>
       </c>
       <c r="X2">
-        <v>-1.937148288569783E-10</v>
+        <v>-1.937040709188358E-10</v>
       </c>
       <c r="Y2">
-        <v>-1.618471938001772E-10</v>
+        <v>-1.618430724436743E-10</v>
       </c>
       <c r="Z2">
-        <v>84.60871947156714</v>
+        <v>84.60871947161206</v>
       </c>
       <c r="AA2">
         <v>-170.3193910162658</v>
       </c>
       <c r="AB2">
-        <v>37.22943985112055</v>
+        <v>37.22943985112049</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>9.696208662707562</v>
+        <v>9.696208662707537</v>
       </c>
       <c r="AE2">
         <v>-142.7892737871882</v>
       </c>
       <c r="AG2">
-        <v>0.9520045753620061</v>
+        <v>0.9520045753620058</v>
       </c>
       <c r="AH2">
-        <v>0.6707651729559317</v>
+        <v>0.6707651729559316</v>
       </c>
       <c r="AI2">
-        <v>0.4216157504340802</v>
+        <v>0.4216157504340798</v>
       </c>
       <c r="AJ2">
-        <v>1.315056832745735</v>
+        <v>1.315056832745734</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -6662,13 +6662,13 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-6.172553624091376</v>
+        <v>-6.172553624091377</v>
       </c>
       <c r="AN2">
         <v>-166.827973412876</v>
       </c>
       <c r="AO2">
-        <v>127.7395623824123</v>
+        <v>127.7395623824122</v>
       </c>
       <c r="AP2">
         <v>-8.930089734159868</v>
@@ -6829,10 +6829,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0004965920471330848</v>
+        <v>0.0004965920471326925</v>
       </c>
       <c r="C2">
-        <v>1.210481473029656</v>
+        <v>1.210481473029655</v>
       </c>
       <c r="D2">
         <v>0.9669780959040256</v>
@@ -6844,13 +6844,13 @@
         <v>1.210751047298469</v>
       </c>
       <c r="G2">
-        <v>0.9664867209022844</v>
+        <v>0.9664867209022846</v>
       </c>
       <c r="H2">
-        <v>0.005734151041794277</v>
+        <v>0.005734151041789747</v>
       </c>
       <c r="I2">
-        <v>13.97743608605453</v>
+        <v>13.97743608605452</v>
       </c>
       <c r="J2">
         <v>11.16570127941322</v>
@@ -6862,37 +6862,37 @@
         <v>13.98054886158785</v>
       </c>
       <c r="M2">
-        <v>11.16002736962265</v>
+        <v>11.16002736962266</v>
       </c>
       <c r="N2">
-        <v>0.001401851070260923</v>
+        <v>0.001401851070261113</v>
       </c>
       <c r="O2">
         <v>10.45747396702612</v>
       </c>
       <c r="P2">
-        <v>5.683293932532262</v>
+        <v>5.683293932532261</v>
       </c>
       <c r="Q2">
-        <v>-3.881184501660371E-09</v>
+        <v>-3.881186650109879E-09</v>
       </c>
       <c r="R2">
-        <v>-7.32959049441802</v>
+        <v>-7.329590494418018</v>
       </c>
       <c r="S2">
-        <v>-4.670482906278895</v>
+        <v>-4.670482906278894</v>
       </c>
       <c r="T2">
-        <v>-0.005370939161869313</v>
+        <v>-0.005370939161864732</v>
       </c>
       <c r="U2">
-        <v>6.607602901287279</v>
+        <v>6.607602901287276</v>
       </c>
       <c r="V2">
-        <v>7.06265571418042</v>
+        <v>7.062655714180419</v>
       </c>
       <c r="W2">
-        <v>-1.894363554376826E-09</v>
+        <v>-1.89437132520029E-09</v>
       </c>
       <c r="X2">
         <v>-7.329590495048787</v>
@@ -6901,10 +6901,10 @@
         <v>-4.670482911810215</v>
       </c>
       <c r="Z2">
-        <v>72.99235436189871</v>
+        <v>72.99235436188486</v>
       </c>
       <c r="AA2">
-        <v>-164.1397217055247</v>
+        <v>-164.1397217055246</v>
       </c>
       <c r="AB2">
         <v>64.6819630293035</v>
@@ -6919,13 +6919,13 @@
         <v>-115.3222920094987</v>
       </c>
       <c r="AG2">
-        <v>0.9680371887624607</v>
+        <v>0.9680371887624606</v>
       </c>
       <c r="AH2">
-        <v>0.8850043739021403</v>
+        <v>0.8850043739021402</v>
       </c>
       <c r="AI2">
-        <v>0.8118943814477216</v>
+        <v>0.8118943814477215</v>
       </c>
       <c r="AJ2">
         <v>1.119236804364414</v>
@@ -6934,10 +6934,10 @@
         <v>0.7414305680639511</v>
       </c>
       <c r="AL2">
-        <v>0.591849827427967</v>
+        <v>0.5918498274279669</v>
       </c>
       <c r="AM2">
-        <v>-2.379415652547</v>
+        <v>-2.379415652546998</v>
       </c>
       <c r="AN2">
         <v>-131.8527891286921</v>
@@ -6946,7 +6946,7 @@
         <v>115.858453197156</v>
       </c>
       <c r="AP2">
-        <v>-5.992544797940921</v>
+        <v>-5.992544797940919</v>
       </c>
       <c r="AQ2">
         <v>-119.1199834958614</v>
@@ -7104,10 +7104,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0004965920471330848</v>
+        <v>0.0004965920471326925</v>
       </c>
       <c r="C2">
-        <v>1.210481473029656</v>
+        <v>1.210481473029655</v>
       </c>
       <c r="D2">
         <v>0.9669780959040256</v>
@@ -7119,13 +7119,13 @@
         <v>1.210751047298469</v>
       </c>
       <c r="G2">
-        <v>0.9664867209022844</v>
+        <v>0.9664867209022846</v>
       </c>
       <c r="H2">
-        <v>0.005734151041794277</v>
+        <v>0.005734151041789747</v>
       </c>
       <c r="I2">
-        <v>13.97743608605453</v>
+        <v>13.97743608605452</v>
       </c>
       <c r="J2">
         <v>11.16570127941322</v>
@@ -7137,37 +7137,37 @@
         <v>13.98054886158785</v>
       </c>
       <c r="M2">
-        <v>11.16002736962265</v>
+        <v>11.16002736962266</v>
       </c>
       <c r="N2">
-        <v>0.001401851070260923</v>
+        <v>0.001401851070261113</v>
       </c>
       <c r="O2">
         <v>10.45747396702612</v>
       </c>
       <c r="P2">
-        <v>5.683293932532262</v>
+        <v>5.683293932532261</v>
       </c>
       <c r="Q2">
-        <v>-3.881184501660371E-09</v>
+        <v>-3.881186650109879E-09</v>
       </c>
       <c r="R2">
-        <v>-7.32959049441802</v>
+        <v>-7.329590494418018</v>
       </c>
       <c r="S2">
-        <v>-4.670482906278895</v>
+        <v>-4.670482906278894</v>
       </c>
       <c r="T2">
-        <v>-0.005370939161869313</v>
+        <v>-0.005370939161864732</v>
       </c>
       <c r="U2">
-        <v>6.607602901287279</v>
+        <v>6.607602901287276</v>
       </c>
       <c r="V2">
-        <v>7.06265571418042</v>
+        <v>7.062655714180419</v>
       </c>
       <c r="W2">
-        <v>-1.894363554376826E-09</v>
+        <v>-1.89437132520029E-09</v>
       </c>
       <c r="X2">
         <v>-7.329590495048787</v>
@@ -7176,10 +7176,10 @@
         <v>-4.670482911810215</v>
       </c>
       <c r="Z2">
-        <v>72.99235436189871</v>
+        <v>72.99235436188486</v>
       </c>
       <c r="AA2">
-        <v>-164.1397217055247</v>
+        <v>-164.1397217055246</v>
       </c>
       <c r="AB2">
         <v>64.6819630293035</v>
@@ -7194,13 +7194,13 @@
         <v>-115.3222920094987</v>
       </c>
       <c r="AG2">
-        <v>0.9680371887624607</v>
+        <v>0.9680371887624606</v>
       </c>
       <c r="AH2">
-        <v>0.8850043739021403</v>
+        <v>0.8850043739021402</v>
       </c>
       <c r="AI2">
-        <v>0.8118943814477216</v>
+        <v>0.8118943814477215</v>
       </c>
       <c r="AJ2">
         <v>1.119236804364414</v>
@@ -7209,10 +7209,10 @@
         <v>0.7414305680639511</v>
       </c>
       <c r="AL2">
-        <v>0.591849827427967</v>
+        <v>0.5918498274279669</v>
       </c>
       <c r="AM2">
-        <v>-2.379415652547</v>
+        <v>-2.379415652546998</v>
       </c>
       <c r="AN2">
         <v>-131.8527891286921</v>
@@ -7221,7 +7221,7 @@
         <v>115.858453197156</v>
       </c>
       <c r="AP2">
-        <v>-5.992544797940921</v>
+        <v>-5.992544797940919</v>
       </c>
       <c r="AQ2">
         <v>-119.1199834958614</v>
@@ -7298,52 +7298,52 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.309686024628784</v>
+        <v>1.309686024628783</v>
       </c>
       <c r="C2">
-        <v>1.309686024628784</v>
+        <v>1.309686024628783</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2.837059479583178</v>
+        <v>2.837059479583173</v>
       </c>
       <c r="F2">
-        <v>45.36885473239915</v>
+        <v>45.36885473239911</v>
       </c>
       <c r="G2">
-        <v>45.36885473239915</v>
+        <v>45.36885473239911</v>
       </c>
       <c r="H2">
-        <v>28.40499517047037</v>
+        <v>28.40499517047036</v>
       </c>
       <c r="I2">
         <v>-25.72916224161305</v>
       </c>
       <c r="J2">
-        <v>28.76520341755295</v>
+        <v>28.76520341755292</v>
       </c>
       <c r="K2">
-        <v>-25.72916225404877</v>
+        <v>-25.72916225404875</v>
       </c>
       <c r="L2">
-        <v>-54.52967391402498</v>
+        <v>-54.52967391402493</v>
       </c>
       <c r="M2">
-        <v>125.4703260859677</v>
+        <v>125.4703260859678</v>
       </c>
       <c r="N2">
-        <v>0.8910570420386132</v>
+        <v>0.8910570420386135</v>
       </c>
       <c r="O2">
-        <v>0.8020156209364411</v>
+        <v>0.8020156209364414</v>
       </c>
       <c r="P2">
-        <v>-9.168679204911154</v>
+        <v>-9.168679204911136</v>
       </c>
       <c r="Q2">
-        <v>-9.529673900180356</v>
+        <v>-9.52967390018034</v>
       </c>
     </row>
   </sheetData>
@@ -7414,16 +7414,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>3.601610081638499</v>
+        <v>3.601610081638498</v>
       </c>
       <c r="C2">
-        <v>3.601610081638499</v>
+        <v>3.601610081638498</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6.838062054648193</v>
+        <v>6.838062054648194</v>
       </c>
       <c r="F2">
         <v>124.7634330090034</v>
@@ -7432,31 +7432,31 @@
         <v>124.7634330090034</v>
       </c>
       <c r="H2">
-        <v>38.85252268584041</v>
+        <v>38.85252268584024</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>22.95972360762198</v>
+        <v>22.95972360762206</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-69.67231644738069</v>
+        <v>-69.67231644738078</v>
       </c>
       <c r="M2">
-        <v>110.327683552612</v>
+        <v>110.3276835526119</v>
       </c>
       <c r="N2">
-        <v>0.3617201835011328</v>
+        <v>0.361720183501132</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-39.09154322526825</v>
+        <v>-39.09154322526815</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -7530,16 +7530,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>3.601610081638499</v>
+        <v>3.601610081638498</v>
       </c>
       <c r="C2">
-        <v>3.601610081638499</v>
+        <v>3.601610081638498</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6.838062054648193</v>
+        <v>6.838062054648194</v>
       </c>
       <c r="F2">
         <v>124.7634330090034</v>
@@ -7548,31 +7548,31 @@
         <v>124.7634330090034</v>
       </c>
       <c r="H2">
-        <v>38.85252268584041</v>
+        <v>38.85252268584024</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>22.95972360762198</v>
+        <v>22.95972360762206</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-69.67231644738069</v>
+        <v>-69.67231644738078</v>
       </c>
       <c r="M2">
-        <v>110.327683552612</v>
+        <v>110.3276835526119</v>
       </c>
       <c r="N2">
-        <v>0.3617201835011328</v>
+        <v>0.361720183501132</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-39.09154322526825</v>
+        <v>-39.09154322526815</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -7646,10 +7646,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.146247392614548</v>
+        <v>1.146247392614549</v>
       </c>
       <c r="C2">
-        <v>1.146247392614548</v>
+        <v>1.146247392614549</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7667,16 +7667,16 @@
         <v>23.64358897071036</v>
       </c>
       <c r="I2">
-        <v>-19.70824627309616</v>
+        <v>-19.70824627309617</v>
       </c>
       <c r="J2">
-        <v>22.03381935746359</v>
+        <v>22.0338193574636</v>
       </c>
       <c r="K2">
-        <v>-19.70824628278307</v>
+        <v>-19.70824628278309</v>
       </c>
       <c r="L2">
-        <v>-52.63434508457833</v>
+        <v>-52.63434508457834</v>
       </c>
       <c r="M2">
         <v>127.3656549154144</v>
@@ -7685,13 +7685,13 @@
         <v>0.8139299031165274</v>
       </c>
       <c r="O2">
-        <v>0.7019303077896066</v>
+        <v>0.7019303077896069</v>
       </c>
       <c r="P2">
-        <v>-9.652735617430441</v>
+        <v>-9.652735617430428</v>
       </c>
       <c r="Q2">
-        <v>-7.634345070499269</v>
+        <v>-7.634345070499253</v>
       </c>
     </row>
   </sheetData>
@@ -7762,10 +7762,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.146247392614548</v>
+        <v>1.146247392614549</v>
       </c>
       <c r="C2">
-        <v>1.146247392614548</v>
+        <v>1.146247392614549</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7783,16 +7783,16 @@
         <v>23.64358897071036</v>
       </c>
       <c r="I2">
-        <v>-19.70824627309616</v>
+        <v>-19.70824627309617</v>
       </c>
       <c r="J2">
-        <v>22.03381935746359</v>
+        <v>22.0338193574636</v>
       </c>
       <c r="K2">
-        <v>-19.70824628278307</v>
+        <v>-19.70824628278309</v>
       </c>
       <c r="L2">
-        <v>-52.63434508457833</v>
+        <v>-52.63434508457834</v>
       </c>
       <c r="M2">
         <v>127.3656549154144</v>
@@ -7801,13 +7801,13 @@
         <v>0.8139299031165274</v>
       </c>
       <c r="O2">
-        <v>0.7019303077896066</v>
+        <v>0.7019303077896069</v>
       </c>
       <c r="P2">
-        <v>-9.652735617430441</v>
+        <v>-9.652735617430428</v>
       </c>
       <c r="Q2">
-        <v>-7.634345070499269</v>
+        <v>-7.634345070499253</v>
       </c>
     </row>
   </sheetData>
@@ -7959,73 +7959,73 @@
         <v>0</v>
       </c>
       <c r="C2">
+        <v>3.709154423744984</v>
+      </c>
+      <c r="D2">
         <v>3.70915442374498</v>
       </c>
-      <c r="D2">
-        <v>3.709154423744977</v>
-      </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
+        <v>3.709154423744982</v>
+      </c>
+      <c r="G2">
         <v>3.709154423744978</v>
       </c>
-      <c r="G2">
-        <v>3.709154423744977</v>
-      </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
+        <v>42.82962610030116</v>
+      </c>
+      <c r="J2">
         <v>42.82962610030111</v>
       </c>
-      <c r="J2">
-        <v>42.82962610030108</v>
-      </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
+        <v>42.82962610030113</v>
+      </c>
+      <c r="M2">
         <v>42.82962610030109</v>
       </c>
-      <c r="M2">
-        <v>42.82962610030107</v>
-      </c>
       <c r="N2">
-        <v>5.210646841809327E-15</v>
+        <v>5.210646841809326E-15</v>
       </c>
       <c r="O2">
-        <v>30.1766144777222</v>
+        <v>30.17661447772224</v>
       </c>
       <c r="P2">
         <v>-15.86847458187514</v>
       </c>
       <c r="Q2">
-        <v>-1.563194052542789E-14</v>
+        <v>-1.563194052542778E-14</v>
       </c>
       <c r="R2">
-        <v>-23.02254452973951</v>
+        <v>-23.02254452973952</v>
       </c>
       <c r="S2">
-        <v>23.02254452985793</v>
+        <v>23.02254452985794</v>
       </c>
       <c r="T2">
-        <v>-5.210646841809228E-15</v>
+        <v>-5.210646841809227E-15</v>
       </c>
       <c r="U2">
-        <v>3.130989834187395</v>
+        <v>3.130989834187393</v>
       </c>
       <c r="V2">
         <v>13.10324558045216</v>
       </c>
       <c r="W2">
-        <v>5.210646841809127E-15</v>
+        <v>-5.210646841809426E-15</v>
       </c>
       <c r="X2">
-        <v>4.986127873134727</v>
+        <v>4.986127873134744</v>
       </c>
       <c r="Y2">
-        <v>-4.986127873130108</v>
+        <v>-4.986127873130076</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -8034,13 +8034,13 @@
         <v>-167.7798457937528</v>
       </c>
       <c r="AB2">
-        <v>12.2201542062399</v>
+        <v>12.22015420623989</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>12.2201542062399</v>
+        <v>12.22015420623989</v>
       </c>
       <c r="AE2">
         <v>-167.7798457937528</v>
@@ -8052,7 +8052,7 @@
         <v>0.7083556674758257</v>
       </c>
       <c r="AH2">
-        <v>0.4804898682203934</v>
+        <v>0.4804898682203931</v>
       </c>
       <c r="AI2">
         <v>1.10000002383429</v>
@@ -8061,10 +8061,10 @@
         <v>0.5500000119158038</v>
       </c>
       <c r="AK2">
-        <v>0.5500000119184837</v>
+        <v>0.5500000119184835</v>
       </c>
       <c r="AL2">
-        <v>5.467361524065793E-13</v>
+        <v>5.387178084710288E-13</v>
       </c>
       <c r="AM2">
         <v>-161.8562887546276</v>
@@ -8073,13 +8073,13 @@
         <v>152.6722796269628</v>
       </c>
       <c r="AO2">
-        <v>5.569769009654518E-13</v>
+        <v>5.44051806583874E-13</v>
       </c>
       <c r="AP2">
         <v>179.999999999954</v>
       </c>
       <c r="AQ2">
-        <v>-179.9999999999594</v>
+        <v>-179.9999999999593</v>
       </c>
     </row>
   </sheetData>
